--- a/División/ULA_División.xlsx
+++ b/División/ULA_División.xlsx
@@ -428,16 +428,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>53.10391784429257</v>
+        <v>53.1039178442926</v>
       </c>
       <c r="C2" s="2">
-        <v>116.9041879918659</v>
+        <v>116.8925786248049</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>62.08070394773779</v>
+        <v>62.07453891899151</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="2">
-        <v>13.78023181088566</v>
+        <v>13.78023181088567</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -482,7 +482,7 @@
         <v>16.15719773895828</v>
       </c>
       <c r="C5" s="2">
-        <v>113.5187888506456</v>
+        <v>113.5187888506457</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
